--- a/diseases/d010/2005-2009.xlsx
+++ b/diseases/d010/2005-2009.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -1457,9 +1454,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -2001,9 +1995,6 @@
       <c r="O9" t="n">
         <v>0</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
@@ -2693,9 +2684,6 @@
       <c r="O13" t="n">
         <v>0</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
@@ -3385,9 +3373,6 @@
       <c r="O17" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
@@ -3929,9 +3914,6 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
@@ -4473,9 +4455,6 @@
       <c r="O23" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
@@ -5017,9 +4996,6 @@
       <c r="O26" t="n">
         <v>1</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0.01906184462995432</v>
       </c>
@@ -5561,9 +5537,6 @@
       <c r="O29" t="n">
         <v>0</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0</v>
       </c>
@@ -6105,9 +6078,6 @@
       <c r="O32" t="n">
         <v>0</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0</v>
       </c>
@@ -6797,9 +6767,6 @@
       <c r="O36" t="n">
         <v>0</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0</v>
       </c>
@@ -7341,9 +7308,6 @@
       <c r="O39" t="n">
         <v>0</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0</v>
       </c>
@@ -7885,9 +7849,6 @@
       <c r="O42" t="n">
         <v>0</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0</v>
       </c>
@@ -8577,9 +8538,6 @@
       <c r="O46" t="n">
         <v>0</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0</v>
       </c>
@@ -9269,9 +9227,6 @@
       <c r="O50" t="n">
         <v>0</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
@@ -9813,9 +9768,6 @@
       <c r="O53" t="n">
         <v>0</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0</v>
       </c>
@@ -10357,9 +10309,6 @@
       <c r="O56" t="n">
         <v>0</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0</v>
       </c>
@@ -10901,9 +10850,6 @@
       <c r="O59" t="n">
         <v>0</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0</v>
       </c>
@@ -11445,9 +11391,6 @@
       <c r="O62" t="n">
         <v>2</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0.03797771334858708</v>
       </c>
@@ -11989,9 +11932,6 @@
       <c r="O65" t="n">
         <v>0</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0</v>
       </c>
@@ -12681,9 +12621,6 @@
       <c r="O69" t="n">
         <v>0</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0</v>
       </c>
@@ -13225,9 +13162,6 @@
       <c r="O72" t="n">
         <v>0</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0</v>
       </c>
@@ -13917,9 +13851,6 @@
       <c r="O76" t="n">
         <v>0</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0</v>
       </c>
@@ -14461,9 +14392,6 @@
       <c r="O79" t="n">
         <v>0</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0</v>
       </c>
@@ -15005,9 +14933,6 @@
       <c r="O82" t="n">
         <v>0</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0</v>
       </c>
@@ -15549,9 +15474,6 @@
       <c r="O85" t="n">
         <v>0</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0</v>
       </c>
@@ -16093,9 +16015,6 @@
       <c r="O88" t="n">
         <v>0</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0</v>
       </c>
@@ -16785,9 +16704,6 @@
       <c r="O92" t="n">
         <v>0</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0</v>
       </c>
@@ -17329,9 +17245,6 @@
       <c r="O95" t="n">
         <v>1</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0.01890820256735574</v>
       </c>
@@ -17873,9 +17786,6 @@
       <c r="O98" t="n">
         <v>0</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0</v>
       </c>
@@ -18417,9 +18327,6 @@
       <c r="O101" t="n">
         <v>0</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>0</v>
       </c>
@@ -18961,9 +18868,6 @@
       <c r="O104" t="n">
         <v>0</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0</v>
       </c>
@@ -19505,9 +19409,6 @@
       <c r="O107" t="n">
         <v>0</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0</v>
       </c>
@@ -20049,9 +19950,6 @@
       <c r="O110" t="n">
         <v>0</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0</v>
       </c>
@@ -20593,9 +20491,6 @@
       <c r="O113" t="n">
         <v>0</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0</v>
       </c>
@@ -21137,9 +21032,6 @@
       <c r="O116" t="n">
         <v>0</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0</v>
       </c>
@@ -21681,9 +21573,6 @@
       <c r="O119" t="n">
         <v>0</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0</v>
       </c>
@@ -22225,9 +22114,6 @@
       <c r="O122" t="n">
         <v>0</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0</v>
       </c>
@@ -22917,9 +22803,6 @@
       <c r="O126" t="n">
         <v>1</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>0.01882042249213636</v>
       </c>
@@ -23461,9 +23344,6 @@
       <c r="O129" t="n">
         <v>1</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="R129" t="n">
         <v>0.01882042249213636</v>
       </c>
@@ -24005,9 +23885,6 @@
       <c r="O132" t="n">
         <v>1</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0.01882042249213636</v>
       </c>
@@ -24549,9 +24426,6 @@
       <c r="O135" t="n">
         <v>1</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>0.01882042249213636</v>
       </c>
@@ -25241,9 +25115,6 @@
       <c r="O139" t="n">
         <v>0</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="R139" t="n">
         <v>0</v>
       </c>
@@ -25933,9 +25804,6 @@
       <c r="O143" t="n">
         <v>0</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>0</v>
       </c>
@@ -26477,9 +26345,6 @@
       <c r="O146" t="n">
         <v>0</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0</v>
       </c>
@@ -27169,9 +27034,6 @@
       <c r="O150" t="n">
         <v>0</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>0</v>
       </c>
@@ -27713,9 +27575,6 @@
       <c r="O153" t="n">
         <v>0</v>
       </c>
-      <c r="Q153" t="n">
-        <v>0</v>
-      </c>
       <c r="R153" t="n">
         <v>0</v>
       </c>
@@ -28257,9 +28116,6 @@
       <c r="O156" t="n">
         <v>0</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>0</v>
       </c>
@@ -28801,9 +28657,6 @@
       <c r="O159" t="n">
         <v>1</v>
       </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
       <c r="R159" t="n">
         <v>0.01873060270490507</v>
       </c>
@@ -29345,9 +29198,6 @@
       <c r="O162" t="n">
         <v>0</v>
       </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
       <c r="R162" t="n">
         <v>0</v>
       </c>
@@ -29889,9 +29739,6 @@
       <c r="O165" t="n">
         <v>0</v>
       </c>
-      <c r="Q165" t="n">
-        <v>0</v>
-      </c>
       <c r="R165" t="n">
         <v>0</v>
       </c>
@@ -30433,9 +30280,6 @@
       <c r="O168" t="n">
         <v>0</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>0</v>
       </c>
@@ -30977,9 +30821,6 @@
       <c r="O171" t="n">
         <v>0</v>
       </c>
-      <c r="Q171" t="n">
-        <v>0</v>
-      </c>
       <c r="R171" t="n">
         <v>0</v>
       </c>
@@ -31669,9 +31510,6 @@
       <c r="O175" t="n">
         <v>1</v>
       </c>
-      <c r="Q175" t="n">
-        <v>0</v>
-      </c>
       <c r="R175" t="n">
         <v>0.01873060270490507</v>
       </c>
@@ -32213,9 +32051,6 @@
       <c r="O178" t="n">
         <v>0</v>
       </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
       <c r="R178" t="n">
         <v>0</v>
       </c>
@@ -32757,9 +32592,6 @@
       <c r="O181" t="n">
         <v>0</v>
       </c>
-      <c r="Q181" t="n">
-        <v>0</v>
-      </c>
       <c r="R181" t="n">
         <v>0</v>
       </c>
@@ -33301,9 +33133,6 @@
       <c r="O184" t="n">
         <v>0</v>
       </c>
-      <c r="Q184" t="n">
-        <v>0</v>
-      </c>
       <c r="R184" t="n">
         <v>0</v>
       </c>
@@ -33845,9 +33674,6 @@
       <c r="O187" t="n">
         <v>0</v>
       </c>
-      <c r="Q187" t="n">
-        <v>0</v>
-      </c>
       <c r="R187" t="n">
         <v>0</v>
       </c>
@@ -34389,9 +34215,6 @@
       <c r="O190" t="n">
         <v>1</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="R190" t="n">
         <v>0.01873060270490507</v>
       </c>
@@ -34931,9 +34754,6 @@
         <v>0</v>
       </c>
       <c r="O193" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q193" t="n">
         <v>0</v>
       </c>
       <c r="R193" t="n">
